--- a/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:43:57+00:00</t>
+    <t>2026-09-02T12:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>FRLMInformant.informant[x].informantOrganisation</t>
+  </si>
+  <si>
+    <t>FRLMOrganisation</t>
   </si>
   <si>
     <t>FRLMInformant.informant[x].informantPersonne[x]</t>
@@ -475,7 +478,9 @@
       <c r="A5" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
@@ -486,7 +491,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -499,14 +504,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -548,7 +553,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -563,7 +568,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -576,7 +581,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -584,25 +589,27 @@
       <c r="A5" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2"/>
     </row>

--- a/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:54:48+00:00</t>
+    <t>2026-09-02T15:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:48:56+00:00</t>
+    <t>2026-09-03T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:02:14+00:00</t>
+    <t>2026-09-03T10:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRInformantLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:35:28+00:00</t>
+    <t>2026-09-04T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
